--- a/results/lendt_adults_fused.xlsx
+++ b/results/lendt_adults_fused.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.98 [0.98, 0.99]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -553,17 +553,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -575,98 +575,130 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>840.00 ± 0.00</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>300.00 ± 0.00</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>540.03 ± 0.17</t>
+          <t>0.99 [0.98, 1.00]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>534.91 ± 30.44</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>539.69 ± 2.58</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>29400</v>
-      </c>
-      <c r="C7" t="n">
-        <v>10500</v>
-      </c>
-      <c r="D7" t="n">
-        <v>18901</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18722</v>
-      </c>
-      <c r="F7" t="n">
-        <v>18889</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>840.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>300.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>540.03 ± 0.17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>534.91 ± 30.44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>539.69 ± 2.58</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>29400</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>10500</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>18901</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>18722</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>18889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>n_total</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>35</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="B10" t="n">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -681,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,17 +788,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.83 [0.80, 0.86]</t>
+          <t>0.83 [0.79, 0.86]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91 [0.89, 0.93]</t>
+          <t>0.91 [0.88, 0.93]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.99]</t>
+          <t>0.97 [0.94, 0.99]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -778,162 +810,194 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.99]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.85]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.91 [0.88, 0.93]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.99]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.00 [0.99, 1.00]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.84 [0.81, 0.88]</t>
+          <t>0.82 [0.78, 0.86]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.91 [0.89, 0.93]</t>
+          <t>0.91 [0.88, 0.94]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 1.00]</t>
+          <t>0.97 [0.94, 0.99]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.96 [0.94, 0.97]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1311.89 ± 902.75</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>508.11 ± 345.63</t>
+          <t>0.84 [0.81, 0.88]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>999.31 ± 547.90</t>
+          <t>0.91 [0.89, 0.93]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>337.88 ± 296.53</t>
+          <t>0.97 [0.94, 1.00]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>660.93 ± 359.86</t>
+          <t>0.96 [0.94, 0.97]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>45916</v>
-      </c>
-      <c r="C7" t="n">
-        <v>17784</v>
-      </c>
-      <c r="D7" t="n">
-        <v>34976</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8109</v>
-      </c>
-      <c r="F7" t="n">
-        <v>17845</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1311.89 ± 902.75</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>508.11 ± 345.63</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>999.31 ± 547.90</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>337.88 ± 296.53</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>660.93 ± 359.86</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>45916</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>17784</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34976</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>8109</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>17845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>n_total</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>35</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="B10" t="n">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
         <v>35</v>
       </c>
     </row>

--- a/results/lendt_adults_fused.xlsx
+++ b/results/lendt_adults_fused.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Laboratory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Free-living" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Laboratory matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Free-living" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Free-living matrix" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,6 +715,892 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>34.90925925925926</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9974074074074074</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.009728833730787922</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9940654360925615</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0004761904761904762</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.00157793689443717</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001018230764242453</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.07407407407407408</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.002116402116402117</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008582487592005968</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005064589754940576</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>35</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001851851851851852</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.291005291005291e-05</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0003130200943438951</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0001604362174242179</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3185185185185185</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0091005291005291</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.01895121625940376</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.002590558545688552</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.01561049965536965</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>34.67962962962963</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9908465608465609</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.01892763155418234</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9843446919214223</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9973484297716995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1004,4 +1892,890 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.79294209144394</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9552941515349608</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04935390029809637</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9357703988191506</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.974817904250771</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.002377179080824089</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.804366966015144e-05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0004574883274085783</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0002690200245327411</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2941527249784862</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01089454536957356</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01773157653185551</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.003880167308701982</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01790892343044514</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5292967199868962</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0196035822217369</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03045554215506066</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.007555770999727512</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.03165139344374628</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3812312845098537</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01411967720406865</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02055066862801917</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.005990103451749013</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0222492509563883</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.31858924947201</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9716078853946669</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0683508983184844</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9427458323074687</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1370761587290638</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005711506613710992</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01537412014345973</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01220342819288209</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5443345917989302</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02268060799162209</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0556586835531665</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.04618320882050729</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.8338405063746</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9952525858964171</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.008468455005921274</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9923435698217267</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9981616019711075</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0758727178145395</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.002167791937558272</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.006648109179383042</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.004451497342570119</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0902867758108635</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.002579622166024672</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005956604669280926</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0005334568712456146</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.004625787460803729</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2314443130671696</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.006612694659061988</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.01378502774418153</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.001877371950275318</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01134801736784866</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.005157040929852199</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0001473440265672057</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0006220592432603353</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0003610288529952581</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5453443973763867</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01558126849646819</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.03636004421584912</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.003091156306416843</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.02807138068651954</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>29.54935167278455</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8442671906509872</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1098515107576978</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8065318764290038</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8820025048729706</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.668702575842042</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1333915021669155</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0895705374530332</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1026229460268235</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1641600583070075</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02576936893693024</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0007362676839122927</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.002167361596474938</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.001480782441256314</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1701551808061598</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.004861576594461709</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.009069717000732168</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00174601979814236</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.007977133390781059</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2377901827181013</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.006794005220517181</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.007006027942801239</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.004387350418538729</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.009200660022495633</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.77382278352773</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.07925207952936372</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05903232241857498</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.05897376728446575</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09953039177426169</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31.79246248401108</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9083560709717451</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.06291117662550685</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8867453256878269</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9299668162556632</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/lendt_adults_fused.xlsx
+++ b/results/lendt_adults_fused.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.99 [0.98, 1.00]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,27 +518,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>1.00 [0.99, 1.00]</t>
         </is>
       </c>
     </row>
@@ -981,16 +981,16 @@
         <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>34.90925925925926</v>
+        <v>34.91111111111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9974074074074074</v>
+        <v>0.9974603174603175</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009728833730787922</v>
+        <v>0.009443544259352491</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9940654360925615</v>
+        <v>0.9942163465077295</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1047,19 +1047,19 @@
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004761904761904762</v>
+        <v>0.0006349206349206349</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00157793689443717</v>
+        <v>0.002151322552303417</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001018230764242453</v>
+        <v>0.001373925787822641</v>
       </c>
     </row>
     <row r="11">
@@ -1080,19 +1080,19 @@
         <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07407407407407408</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002116402116402117</v>
+        <v>0.001904761904761905</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008582487592005968</v>
+        <v>0.007628584048087617</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005064589754940576</v>
+        <v>0.004525272211246011</v>
       </c>
     </row>
     <row r="12">
@@ -1476,19 +1476,19 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001851851851851852</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5.291005291005291e-05</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003130200943438951</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0001604362174242179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1542,19 +1542,19 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3185185185185185</v>
+        <v>0.3851851851851851</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0091005291005291</v>
+        <v>0.011005291005291</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01895121625940376</v>
+        <v>0.0250833471344285</v>
       </c>
       <c r="H25" t="n">
-        <v>0.002590558545688552</v>
+        <v>0.00238885979439462</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01561049965536965</v>
+        <v>0.01962172221618739</v>
       </c>
     </row>
     <row r="26">
@@ -1575,19 +1575,19 @@
         <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>34.67962962962963</v>
+        <v>34.61481481481482</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9908465608465609</v>
+        <v>0.9889947089947092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01892763155418234</v>
+        <v>0.02508334713442851</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9843446919214223</v>
+        <v>0.9803782777838128</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9973484297716995</v>
+        <v>0.9976111402056056</v>
       </c>
     </row>
   </sheetData>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.83 [0.79, 0.86]</t>
+          <t>0.82 [0.79, 0.86]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91 [0.88, 0.93]</t>
+          <t>0.90 [0.88, 0.93]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.86]</t>
+          <t>0.81 [0.77, 0.85]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.84 [0.81, 0.88]</t>
+          <t>0.85 [0.81, 0.88]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.91 [0.89, 0.93]</t>
+          <t>0.91 [0.88, 0.93]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1968,19 +1968,19 @@
         <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>25.79294209144394</v>
+        <v>25.79394116727066</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9552941515349608</v>
+        <v>0.9553311543433578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04935390029809637</v>
+        <v>0.04949760198309867</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9357703988191506</v>
+        <v>0.9357505551342434</v>
       </c>
       <c r="I2" t="n">
-        <v>0.974817904250771</v>
+        <v>0.9749117535524722</v>
       </c>
     </row>
     <row r="3">
@@ -2067,19 +2067,19 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5292967199868962</v>
+        <v>0.5465493662271255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0196035822217369</v>
+        <v>0.02024256911952316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03045554215506066</v>
+        <v>0.03001410572270051</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007555770999727512</v>
+        <v>0.008369384334190386</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03165139344374628</v>
+        <v>0.03211575390485594</v>
       </c>
     </row>
     <row r="6">
@@ -2100,19 +2100,19 @@
         <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3812312845098537</v>
+        <v>0.3629795624429037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01411967720406865</v>
+        <v>0.01344368749788532</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02055066862801917</v>
+        <v>0.02088446649165628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005990103451749013</v>
+        <v>0.005182067708527997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0222492509563883</v>
+        <v>0.02170530728724265</v>
       </c>
     </row>
     <row r="7">
@@ -2166,19 +2166,19 @@
         <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>23.31858924947201</v>
+        <v>23.19872187160048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9716078853946669</v>
+        <v>0.9666134113166865</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0683508983184844</v>
+        <v>0.07226472661573935</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9427458323074687</v>
+        <v>0.9360986934823009</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.9971281291510722</v>
       </c>
     </row>
     <row r="9">
@@ -2232,19 +2232,19 @@
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1370761587290638</v>
+        <v>0.1019884394308182</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005711506613710992</v>
+        <v>0.004249518309617425</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01537412014345973</v>
+        <v>0.01407236532626883</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01220342819288209</v>
+        <v>0.01019175703802021</v>
       </c>
     </row>
     <row r="11">
@@ -2265,19 +2265,19 @@
         <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5443345917989302</v>
+        <v>0.6992896889687081</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02268060799162209</v>
+        <v>0.02913707037369617</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0556586835531665</v>
+        <v>0.05977803795123855</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.003895018736598463</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04618320882050729</v>
+        <v>0.05437912201079388</v>
       </c>
     </row>
     <row r="12">
@@ -2397,19 +2397,19 @@
         <v>35</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0758727178145395</v>
+        <v>0.07455113191145581</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002167791937558272</v>
+        <v>0.002130032340327309</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006648109179383042</v>
+        <v>0.006656804230511851</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004451497342570119</v>
+        <v>0.004416724599905459</v>
       </c>
     </row>
     <row r="16">
@@ -2430,19 +2430,19 @@
         <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0902867758108635</v>
+        <v>0.09160836171394721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002579622166024672</v>
+        <v>0.002617381763255634</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005956604669280926</v>
+        <v>0.005943946585777043</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005334568712456146</v>
+        <v>0.0005755646722943714</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004625787460803729</v>
+        <v>0.004659198854216897</v>
       </c>
     </row>
     <row r="17">
@@ -2562,19 +2562,19 @@
         <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>29.54935167278455</v>
+        <v>29.65152020239912</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8442671906509872</v>
+        <v>0.8471862914971177</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1098515107576978</v>
+        <v>0.1061931755666256</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8065318764290038</v>
+        <v>0.810707659381846</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8820025048729706</v>
+        <v>0.8836649236123894</v>
       </c>
     </row>
     <row r="21">
@@ -2595,19 +2595,19 @@
         <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>4.668702575842042</v>
+        <v>4.566534046227471</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1333915021669155</v>
+        <v>0.1304724013207849</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0895705374530332</v>
+        <v>0.08691810622901723</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1026229460268235</v>
+        <v>0.1006149871850228</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1641600583070075</v>
+        <v>0.1603298154565469</v>
       </c>
     </row>
     <row r="22">
@@ -2661,19 +2661,19 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1701551808061598</v>
+        <v>0.1649126989458574</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004861576594461709</v>
+        <v>0.004711791398453067</v>
       </c>
       <c r="G23" t="n">
-        <v>0.009069717000732168</v>
+        <v>0.009103572699732554</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00174601979814236</v>
+        <v>0.001584604762624251</v>
       </c>
       <c r="I23" t="n">
-        <v>0.007977133390781059</v>
+        <v>0.007838978034281883</v>
       </c>
     </row>
     <row r="24">
@@ -2694,19 +2694,19 @@
         <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2377901827181013</v>
+        <v>0.2517350924710008</v>
       </c>
       <c r="F24" t="n">
-        <v>0.006794005220517181</v>
+        <v>0.007192431213457167</v>
       </c>
       <c r="G24" t="n">
-        <v>0.007006027942801239</v>
+        <v>0.007596759053205148</v>
       </c>
       <c r="H24" t="n">
-        <v>0.004387350418538729</v>
+        <v>0.004582853175211518</v>
       </c>
       <c r="I24" t="n">
-        <v>0.009200660022495633</v>
+        <v>0.009802009251702815</v>
       </c>
     </row>
     <row r="25">
@@ -2727,19 +2727,19 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2.77382278352773</v>
+        <v>2.878878786742667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07925207952936372</v>
+        <v>0.08225367962121906</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05903232241857498</v>
+        <v>0.05463266026756503</v>
       </c>
       <c r="H25" t="n">
-        <v>0.05897376728446575</v>
+        <v>0.06348670420358719</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09953039177426169</v>
+        <v>0.1010206550388509</v>
       </c>
     </row>
     <row r="26">
@@ -2760,19 +2760,19 @@
         <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>31.79246248401108</v>
+        <v>31.67870405290354</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9083560709717451</v>
+        <v>0.9051058300829584</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06291117662550685</v>
+        <v>0.05952123487763082</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8867453256878269</v>
+        <v>0.8846595705322632</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9299668162556632</v>
+        <v>0.9255520896336537</v>
       </c>
     </row>
   </sheetData>
